--- a/meal_solutions.xlsx
+++ b/meal_solutions.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S226"/>
+  <dimension ref="A1:S247"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.0" customWidth="true"/>
@@ -21141,6 +21141,1947 @@
         </is>
       </c>
     </row>
+    <row r="227" customHeight="true" ht="20.0">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>20250324_141658_1</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>糙薏仁(113g), 雪白菇(92g), 花菇(80g), 僧帽肌(52g), 猪绞肉(90％瘦肉率)(50g)</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (718/760)</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>0.91 (88.9/97.6)</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>1.12 (40.2/36.0)</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>0.90 (22.5/25.1)</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>0.06 (21/385)</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>1.01 (1487/1470)</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>0.14 (58/420)</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>2.54 (310/122)</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>28.2%</t>
+        </is>
+      </c>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" customHeight="true" ht="20.0">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>20250324_141658_2</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>糙薏仁(113g), 日本茼蒿(有机)(128g), 黑柿番茄(125g), 冬瓜平均值(138g), 雪白菇(92g), 花菇(80g), 僧帽肌(52g), 红凤菜(112g), 洋菇(53g)</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>0.96 (731/760)</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>1.14 (111.3/97.6)</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>1.07 (38.5/36.0)</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>0.66 (16.5/25.1)</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>0.82 (316/385)</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>1.76 (2586/1470)</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>0.68 (286/420)</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>3.54 (433/122)</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>59.5%</t>
+        </is>
+      </c>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>20.6%</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="N228" s="2"/>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" customHeight="true" ht="20.0">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>20250324_141658_3</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>米胚芽(103g), 鸡蛋白平均值(38g), 干木耳(红耳仔)(50g), 海带卷(30g), 鲨鱼翅(50g), 鸡水煮蛋白(36g)</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (721/760)</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>1.02 (100.0/97.6)</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>1.45 (52.0/36.0)</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>0.53 (13.4/25.1)</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>0.50 (191/385)</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>1.17 (1721/1470)</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>0.65 (274/420)</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>5.48 (671/122)</t>
+        </is>
+      </c>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
+          <t>54.9%</t>
+        </is>
+      </c>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>16.5%</t>
+        </is>
+      </c>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" customHeight="true" ht="20.0">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>20250324_142111_1</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>糙籼米浆(100g), 鲍鱼(52g), 白对虾(小)(51g), 干木耳(红耳仔)(50g), 白凤豆(台湾)(50g), 金喜菇(51g), 鸡腿菇(51g), 白芝麻(熟)(29g)</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>0.99 (749/760)</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>1.05 (102.9/97.6)</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>1.34 (48.1/36.0)</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>0.86 (21.5/25.1)</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>0.67 (257/385)</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>1.14 (1673/1470)</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>0.62 (259/420)</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>3.27 (400/122)</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>24.3%</t>
+        </is>
+      </c>
+      <c r="N230" s="2"/>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" customHeight="true" ht="20.0">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>20250324_142111_2</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>台湾藜(红)(带壳)(100g), 蜗牛肉(54g), 乌骨鸡蛋黄(53g), 雪里蕻(148g), 冷冻麻竹笋(130g), 甜椒(橙皮)(151g), 西洋芹菜(165g)</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>0.96 (732/760)</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>0.91 (88.9/97.6)</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>1.04 (37.4/36.0)</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>1.04 (26.1/25.1)</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>1.63 (626/385)</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>2.63 (3863/1470)</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>0.63 (263/420)</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>2.91 (356/122)</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
+          <t>48.1%</t>
+        </is>
+      </c>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>31.7%</t>
+        </is>
+      </c>
+      <c r="N231" s="2"/>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" customHeight="true" ht="20.0">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>20250324_142111_3</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>玉米胚芽(100g), 鹊豆荚(50g), 小白菜(土植)(10月取样)(118g), 富珍茸(75g), 喜来菇(52g), 乌骨鸡蛋黄(53g), 马拉巴笛鲷(63g)</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>0.91 (694/760)</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>0.97 (94.5/97.6)</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>1.05 (37.7/36.0)</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>0.72 (18.1/25.1)</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>0.64 (246/385)</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>0.78 (1142/1470)</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>0.47 (195/420)</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>0.81 (99/122)</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>54.7%</t>
+        </is>
+      </c>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="N232" s="2"/>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" customHeight="true" ht="20.0">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>20250324_180837_1</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>米胚芽(100g), 冷冻毛豆仁(57g), 舞菇(60g)</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>0.82 (620/760)</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>0.81 (79.5/97.6)</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>0.88 (31.6/36.0)</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>0.83 (20.9/25.1)</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>0.30 (114/385)</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>1.41 (2074/1470)</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>0.60 (250/420)</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>6.31 (772/122)</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>50.2%</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>29.8%</t>
+        </is>
+      </c>
+      <c r="N233" s="2"/>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" customHeight="true" ht="20.0">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>20250324_180837_2</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>白饭(124g), 红扁豆仁(58g), 鸭肠(52g), 太空鸭(67g), 蒸蛋(市售)(44g), 马铃薯(32g), 海带梗(57g)</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>0.97 (734/760)</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (93.1/97.6)</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>1.08 (39.0/36.0)</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>0.92 (23.0/25.1)</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>0.18 (68/385)</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>0.57 (835/1470)</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>0.65 (272/420)</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>0.59 (72/122)</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>21.2%</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>28.2%</t>
+        </is>
+      </c>
+      <c r="N234" s="2"/>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" customHeight="true" ht="20.0">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>20250324_180837_3</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>稉米(台农71号)(100g), 松茸白菇(56g), 乌骨鸡蛋(34g), 日本花鲈(2月)(50g), 鲭鱼(烤,150度,20分)(50g), 蒸蛋(市售)(44g)</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (720/760)</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>0.87 (85.0/97.6)</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>1.08 (38.8/36.0)</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>1.01 (25.3/25.1)</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>0.13 (51/385)</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>0.51 (745/1470)</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>0.64 (267/420)</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>0.50 (60/122)</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>47.0%</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>31.5%</t>
+        </is>
+      </c>
+      <c r="N235" s="2"/>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" customHeight="true" ht="20.0">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>20250324_180859_1</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>双色水果玉米(100g), 豌豆荚(62g), 舞菇(76g), 翻车鲀鱼皮(52g), 百合鳞片(165g), 僧帽肌(52g), 天贝(黄豆)(50g), 油炸脱水甘藷(27g)</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>0.97 (739/760)</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>1.03 (100.6/97.6)</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>1.08 (38.9/36.0)</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>0.90 (22.5/25.1)</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>0.38 (147/385)</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>1.41 (2074/1470)</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>0.54 (225/420)</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>1.30 (159/122)</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" customHeight="true" ht="20.0">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>20250324_180859_2</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>红藜麦(123g), 青江菜(土植)(1月取样)(102g), 鸡蛋(黄壳)(50g), 青葱平均值(137g), 鳞网带䲠切片(51g)</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (723/760)</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>0.96 (93.8/97.6)</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>0.92 (33.0/36.0)</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>0.96 (24.1/25.1)</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>0.49 (186/385)</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>1.07 (1577/1470)</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>0.46 (195/420)</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>2.02 (247/122)</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>51.8%</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N237" s="2"/>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" customHeight="true" ht="20.0">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>20250324_180859_3</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>发芽稉米(台稉71号)(100g), 粉豆荚(82g), 甘蓝平均值(105g), 猪血(74g), 鸭胗(74g), 鸡蛋(黄壳)(59g), 猪颈肉(52g)</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (722/760)</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>0.87 (85.2/97.6)</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>1.29 (46.3/36.0)</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>0.85 (21.2/25.1)</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>0.34 (132/385)</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>0.66 (976/1470)</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>0.76 (319/420)</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>1.41 (173/122)</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>47.5%</t>
+        </is>
+      </c>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>25.8%</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="N238" s="2"/>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" customHeight="true" ht="20.0">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>20250324_181249_1</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>高筋面粉(2021年取样)(100g), 敏豆荚(50g), 鸡蛋(黄壳)(25g), 猪上肩肉(54g), 橙蕃茄(121g), 越瓜(139g), 鲍鱼菇(80g), 甘蓝(圆球形)(2021年取样)(100g), 芹菜(100g), 清腿平均值(54g)</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>0.99 (753/760)</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>1.04 (102.0/97.6)</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>1.28 (46.1/36.0)</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>0.71 (17.7/25.1)</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>0.58 (221/385)</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>1.22 (1796/1470)</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>0.58 (244/420)</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>1.16 (142/122)</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>54.3%</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>24.5%</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>21.2%</t>
+        </is>
+      </c>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" customHeight="true" ht="20.0">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>20250324_181249_2</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>稉米(台农71号)(106g), 银鲳(12月)(50g), 熟猪肚(77g), 千宝菜(123g), 青江菜(水耕)(7月取样)(160g), 鸡水煮蛋黄(36g)</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>0.94 (716/760)</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>0.96 (93.6/97.6)</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>1.13 (40.6/36.0)</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>0.81 (20.4/25.1)</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>0.99 (379/385)</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>0.84 (1239/1470)</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>0.40 (166/420)</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>1.05 (128/122)</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>22.6%</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>25.5%</t>
+        </is>
+      </c>
+      <c r="N240" s="2"/>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" customHeight="true" ht="20.0">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>20250324_181249_3</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>黑麦片(100g), 鸭蛋(34g), 鸡胸骨汤(83g), 火炭母草(100g), 红毛苔(49g), 姬松茸(59g), 鸡水煮蛋黄(36g)</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (719/760)</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>1.04 (102.0/97.6)</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>1.19 (42.6/36.0)</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>0.75 (18.8/25.1)</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>0.92 (353/385)</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>2.20 (3227/1470)</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>0.52 (219/420)</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>2.71 (332/122)</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>22.8%</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="N241" s="2"/>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" customHeight="true" ht="20.0">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>20250424_175844_1</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>籼米(台中在来2号)(100g), 鸡水煮蛋(25g), 昭和草(100g), 包心芥菜(124g), 青江菜(水耕)(7月取样)(138g), 双髻鲨腹肉(54g), 猪去皮腹脇肉(51g), 丝瓜(105g)</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (720/760)</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>0.93 (91.2/97.6)</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>1.11 (40.1/36.0)</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>0.86 (21.6/25.1)</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>0.83 (318/385)</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>1.31 (1926/1470)</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>0.42 (176/420)</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>1.27 (155/122)</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>50.7%</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>22.3%</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>27.1%</t>
+        </is>
+      </c>
+      <c r="N242" s="2"/>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" customHeight="true" ht="20.0">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>20250424_175844_2</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>稉型糯米(台稉糯1号)(100g), 豌豆仁(54g), 鲽鱼切片(71g), 鸡水煮蛋(31g), 刺鲳(含皮)(50g)</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>0.96 (728/760)</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>0.95 (92.8/97.6)</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>1.07 (38.5/36.0)</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>0.85 (21.4/25.1)</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>0.19 (71/385)</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>0.51 (742/1470)</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>0.47 (198/420)</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>1.15 (140/122)</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>51.7%</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="N243" s="2"/>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" customHeight="true" ht="20.0">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>20250424_175844_3</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>糙籼米浆(100g), 昭和草(125g), 冬瓜(2022年取样)(101g), 黑芝麻(熟)(2022年取样)(53g), 鹰嘴豆(51g), 丝瓜(100g), 日本对虾(大)(73g)</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>0.93 (710/760)</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>0.69 (67.4/97.6)</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>1.16 (41.7/36.0)</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>1.35 (33.9/25.1)</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>2.31 (888/385)</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>1.44 (2112/1470)</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>0.55 (230/420)</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>2.94 (359/122)</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>22.5%</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>41.1%</t>
+        </is>
+      </c>
+      <c r="N244" s="2"/>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" customHeight="true" ht="20.0">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>20250811_124406_1</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>白糯米粉(100g), 葵扇白菜(117g), 绿芦笋(短型)(126g), 鸡脚(肉鸡)(59g), 骨腿(肉鸡)(51g), 猪心(51g)</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>0.96 (691/724)</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>0.98 (91.0/93.0)</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>1.08 (37.1/34.2)</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>0.84 (20.0/23.9)</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>0.49 (178/366)</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>0.63 (881/1400)</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>0.54 (217/400)</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>1.89 (220/116)</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>52.5%</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>26.0%</t>
+        </is>
+      </c>
+      <c r="N245" s="2"/>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="Q245" s="2"/>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" customHeight="true" ht="20.0">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>20250811_124406_2</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>红糯糙米(100g), 仿刺参(50g), 二节翅(肉鸡)(54g), 冷冻木耳(61g), 去骨牛小排(50g), 黄金菾菜(128g)</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>0.97 (699/724)</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>0.91 (84.3/93.0)</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>1.02 (35.1/34.2)</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>1.02 (24.4/23.9)</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>0.40 (144/366)</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>0.81 (1139/1400)</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>0.57 (229/400)</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>2.22 (258/116)</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>48.4%</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>31.5%</t>
+        </is>
+      </c>
+      <c r="N246" s="2"/>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="Q246" s="2"/>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="S246" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" customHeight="true" ht="20.0">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>20250811_124406_3</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>发芽稉米(台稉71号)(100g), 小白菜(有机)(1月取样)(100g), 鸡脚(肉鸡)(59g), 骨腿(肉鸡)(51g), 猪心(51g)</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>0.91 (656/724)</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>0.83 (76.9/93.0)</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>1.05 (36.1/34.2)</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>0.94 (22.4/23.9)</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>0.58 (214/366)</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>0.50 (696/1400)</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>0.60 (240/400)</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>1.36 (158/116)</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>47.0%</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>22.1%</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>30.9%</t>
+        </is>
+      </c>
+      <c r="N247" s="2"/>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="Q247" s="2"/>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
